--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1002.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1002.xlsx
@@ -507,7 +507,7 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>・会場: Peridot 201-203, Singapore EXPO。使用言語: 英語。Zoom Webinar による双方向ハイブリッド（オンライン登壇の可能性: UNDP・WMO＝未登録）。AI通訳（日本語）は神戸側が監視。
-・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。仕様（プレミアムプラン、pocketalk.jp/sentio/lineup・取扱説明書 10/1 確認）: 通訳の連続利用は 1 回 90 分、月の累計は無制限、共有可能人数 50 名、共有 URL/QR は共有開始から 6 時間で自動破棄。カンファレンスプランは連続無制限・URL 固定・50 名超も可（見積り制、リハーサル無償）。→ 運用: 通訳は 90 分ごとに藤本が再開（28 日 14:08 頃＝RT 13 番目の発言者の後、29 日 10:20 頃＝TS 発表 3 と 4 の間、11:40 頃＝閉会前）。共有 URL は本番用を 28 日 12:40、29 日 08:55 に開始する（08:00 の接続テストで開いた共有は必ず終了。6 時間で URL が破棄されるため、テストの共有をそのまま使うと 14:00 頃に切れる）。通訳を再開しても同じ共有 URL が維持されるかは神戸のリハーサルで検証（維持されるなら QR の再掲示は不要。されない場合は再開時に新 QR＝PPT 08b／16b を 20 秒表示し MC が再読込みを案内）。同時閲覧 50 名を超える見込み（日本語字幕の需要が多い場合）ならカンファレンスプランの見積りを取る。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
+・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。QR/URL は共有開始の操作で初めて発行されるので、事前印刷はできない（当日、共有開始直後にスライド貼付と案内カード印刷）。仕様（プレミアムプラン、pocketalk.jp/sentio/lineup・取扱説明書 10/1 確認）: 通訳の連続利用は 1 回 90 分、月の累計は無制限、共有可能人数 50 名、共有 URL/QR は共有開始から 6 時間で自動破棄。カンファレンスプランは連続無制限・URL 固定・50 名超も可（見積り制、リハーサル無償）。→ 運用: 通訳は 90 分ごとに藤本が再開（28 日 14:08 頃＝RT 13 番目の発言者の後、29 日 10:20 頃＝TS 発表 3 と 4 の間、11:40 頃＝閉会前）。共有 URL は本番用を 28 日 12:40、29 日 08:55 に開始する（08:00 の接続テストで開いた共有は必ず終了。6 時間で URL が破棄されるため、テストの共有をそのまま使うと 14:00 頃に切れる）。通訳を再開しても同じ共有 URL が維持されるかは神戸のリハーサルで検証（維持されるなら QR の再掲示は不要。されない場合は再開時に新 QR＝PPT 08b／16b を 20 秒表示し MC が再読込みを案内）。同時閲覧 50 名を超える見込み（日本語字幕の需要が多い場合）ならカンファレンスプランの見積りを取る。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 ポケトークライブ（Sentio）の本番の共有 URL を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に再開）。QR は PPT 08 とテーブル上の案内カードで掲示。</t>
+          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 ポケトークライブ（Sentio）の本番の共有 URL を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に再開）。QR は共有開始後にしか発行されないため事前印刷は不可。12:40 の共有開始直後に藤本が QR を PPT 08 に貼り、田中がポータブルプリンターでテーブル用案内カードを印刷して 12:45 までに配る（間に合わなければ PPT 08 の掲示のみ）。</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -4224,7 +4224,7 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>【ポケトークライブ】通訳は 08:55 開始分が 10:25 で 90 分に達するため、発表 3 件目（10:05-10:20）の後に藤本が通訳を再開。共有 URL が維持されない場合のみ新 QR スライド（PPT 16b）を 20 秒表示し Moderator が再読込みを案内。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
+          <t>【ポケトークライブ】通訳は 08:55 開始分が 10:25 で 90 分に達するため、発表 3 件目（10:05-10:20）の後に藤本が通訳を再開。共有 URL が維持されない場合のみ新 QR スライド（PPT 16b）を 20 秒表示し Moderator が再読込みを案内。29 日の QR も 08:55 の共有開始後に発行されるため、PPT 08 への貼付と案内カードの印刷は 08:55〜09:00 に行う（RT Part 2 開始時は PPT 掲示のみでも可）。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>

--- a/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1002.xlsx
+++ b/reports/acdr2026_staff_deployment/進行シナリオ_0929/ACDR2026_進行シナリオ_Opening_RT_TS_CS_案1002.xlsx
@@ -507,7 +507,7 @@
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>・会場: Peridot 201-203, Singapore EXPO。使用言語: 英語。Zoom Webinar による双方向ハイブリッド（オンライン登壇の可能性: UNDP・WMO＝未登録）。AI通訳（日本語）は神戸側が監視。
-・AI 翻訳字幕＝ポケトークライブ（Sentio）。参加者はスマホで QR（PPT 08 に掲示）を読み、各自の言語で字幕を見る。QR/URL は共有開始の操作で初めて発行されるので、事前印刷はできない（当日、共有開始直後にスライド貼付と案内カード印刷）。仕様（プレミアムプラン、pocketalk.jp/sentio/lineup・取扱説明書 10/1 確認）: 通訳の連続利用は 1 回 90 分、月の累計は無制限、共有可能人数 50 名、共有 URL/QR は共有開始から 6 時間で自動破棄。カンファレンスプランは連続無制限・URL 固定・50 名超も可（見積り制、リハーサル無償）。→ 運用: 通訳は 90 分ごとに藤本が再開（28 日 14:08 頃＝RT 13 番目の発言者の後、29 日 10:20 頃＝TS 発表 3 と 4 の間、11:40 頃＝閉会前）。共有 URL は本番用を 28 日 12:40、29 日 08:55 に開始する（08:00 の接続テストで開いた共有は必ず終了。6 時間で URL が破棄されるため、テストの共有をそのまま使うと 14:00 頃に切れる）。通訳を再開しても同じ共有 URL が維持されるかは神戸のリハーサルで検証（維持されるなら QR の再掲示は不要。されない場合は再開時に新 QR＝PPT 08b／16b を 20 秒表示し MC が再読込みを案内）。同時閲覧 50 名を超える見込み（日本語字幕の需要が多い場合）ならカンファレンスプランの見積りを取る。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
+・AI 翻訳＝ポケトークライブ（Sentio）。ホストは神戸（中村）が Zoom の音声を入力して運用する。参加者は QR（PPT 08 と卓上カード）を読み、自分の携帯や PC で翻訳言語を選んで読む。会場スクリーンへの字幕投影はしない。QR/URL は神戸が共有を開始した時点で発行されるので事前印刷はできない（共有開始直後に神戸が QR 画像を現地へ送り、現地でスライド貼付と案内カード印刷）。仕様（プレミアムプラン、pocketalk.jp/sentio/lineup・取扱説明書 10/1 確認）: 通訳の連続利用は 1 回 90 分、月の累計は無制限、共有可能人数 50 名、共有 URL/QR は共有開始から 6 時間で自動破棄。カンファレンスプランは連続無制限・URL 固定・50 名超も可（見積り制、リハーサル無償）。→ 運用: 通訳は 90 分ごとに藤本が再開（28 日 14:08 頃＝RT 13 番目の発言者の後、29 日 10:20 頃＝TS 発表 3 と 4 の間、11:40 頃＝閉会前）。共有 URL は本番用を 28 日 12:40、29 日 08:55 に開始する（08:00 の接続テストで開いた共有は必ず終了。6 時間で URL が破棄されるため、テストの共有をそのまま使うと 14:00 頃に切れる）。通訳を再開しても同じ共有 URL が維持されるかは神戸のリハーサルで検証（維持されるなら QR の再掲示は不要。されない場合は再開時に新 QR＝PPT 08b／16b を 20 秒表示し MC が再読込みを案内）。同時閲覧 50 名を超える見込み（日本語字幕の需要が多い場合）ならカンファレンスプランの見積りを取る。担当: 現地一次対応 藤本、設定 中村（神戸）。</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 ポケトークライブ（Sentio）の本番の共有 URL を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に再開）。QR は共有開始後にしか発行されないため事前印刷は不可。12:40 の共有開始直後に藤本が QR を PPT 08 に貼り、田中がポータブルプリンターでテーブル用案内カードを印刷して 12:45 までに配る（間に合わなければ PPT 08 の掲示のみ）。</t>
+          <t>昼食（Hall 3, 11:45-12:45）から参加者がPeridotへ戻る。VIP（Commissioner、林副大臣、三浦センター長）は12:40までに着席。12:40 神戸（中村）が Sentio の共有を開始し通訳を開始（共有 URL は 6 時間有効、通訳は 90 分で再開が必要 → 14:08 頃に神戸が再開）。QR は共有開始後にしか発行されないため事前印刷は不可。共有開始直後に神戸から WhatsApp で届く QR 画像を藤本が PPT 08 に貼り、田中がポータブルプリンターで卓上の案内カードを印刷して 12:45 までに配る（間に合わなければ PPT 08 の掲示のみ）。参加者は各自の携帯や PC で言語を選ぶ。</t>
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
@@ -1355,7 +1355,7 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>【ポケトークライブ】通訳は 12:40 開始分が 14:10 で 90 分に達するため、13 番目の発言者（14:03-14:08 枠）の後に藤本が通訳を再開。共有 URL が維持されない場合のみ、池田が新 QR スライド（PPT 08b）を 20 秒表示し MC が「Please scan the new QR code for live translation」と一言。Moderator: SCDF（LTC Chen Yong Kai）単独（Co-Moderator は置かない: Gerry・吉田 9/30 合意、2025 も喜多参事官単独）。ADRC 運営: 吉田（PIC・進行補助・ベル）、Gerry（ノート・サマリー）、池田（PC・スクリーン）、荒木田（AV/Zoom）。</t>
+          <t>【ポケトークライブ】通訳は 12:40 開始分が 14:10 で 90 分に達するため、13 番目の発言者（14:03-14:08 枠）の後に神戸（中村）が通訳を再開（藤本が WhatsApp で合図）。共有 URL が維持されない場合のみ、池田が新 QR スライド（PPT 08b）を 20 秒表示し MC が「Please scan the new QR code for live translation」と一言。Moderator: SCDF（LTC Chen Yong Kai）単独（Co-Moderator は置かない: Gerry・吉田 9/30 合意、2025 も喜多参事官単独）。ADRC 運営: 吉田（PIC・進行補助・ベル）、Gerry（ノート・サマリー）、池田（PC・スクリーン）、荒木田（AV/Zoom）。</t>
         </is>
       </c>
       <c r="G16" s="6" t="n"/>
@@ -4224,7 +4224,7 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>【ポケトークライブ】通訳は 08:55 開始分が 10:25 で 90 分に達するため、発表 3 件目（10:05-10:20）の後に藤本が通訳を再開。共有 URL が維持されない場合のみ新 QR スライド（PPT 16b）を 20 秒表示し Moderator が再読込みを案内。29 日の QR も 08:55 の共有開始後に発行されるため、PPT 08 への貼付と案内カードの印刷は 08:55〜09:00 に行う（RT Part 2 開始時は PPT 掲示のみでも可）。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
+          <t>【ポケトークライブ】通訳は 08:55 開始分が 10:25 で 90 分に達するため、発表 3 件目（10:05-10:20）の後に神戸（中村）が通訳を再開（藤本が WhatsApp で合図）。共有 URL が維持されない場合のみ新 QR スライド（PPT 16b）を 20 秒表示し Moderator が再読込みを案内。29 日の QR も 08:55 に神戸が共有を開始した後に届くため、PPT 08 への貼付と案内カードの印刷は 08:55〜09:00 に行う（RT Part 2 開始時は PPT 掲示のみでも可）。Moderator: LTC Chen Yong Kai（SCDF）。Co-Chair: Dr. Mizan Bisri（ADRC/ADPC）。PIC: 池田。AV/Zoom: 荒木田。カメラ・フロア: 塩見。配分（rev1.0）: 紹介5分＋発表15分×6＋質疑15分＋まとめ10分。</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>
@@ -4931,7 +4931,7 @@
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>所要15分。11:40 頃にポケトークライブの通訳を再開（10:20 再開分が 11:50 で 90 分に達するため）。共有 URL が維持されない場合のみ新 QR を PPT 20 に掲示。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
+          <t>所要15分。11:40 頃に神戸（中村）がポケトークライブの通訳を再開（10:20 再開分が 11:50 で 90 分に達するため）。共有 URL が維持されない場合のみ新 QR を PPT 20 に掲示。Summary（宮木所長＝Executive Director）6分＋閉会挨拶 2名×3分（三浦センター長＝Chairman、SCDF 代表【TBC】）＋MC連絡3分。</t>
         </is>
       </c>
       <c r="G28" s="6" t="n"/>
